--- a/10-12/Stock Daily 2026-10-12.xlsx
+++ b/10-12/Stock Daily 2026-10-12.xlsx
@@ -1049,7 +1049,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="257">
+  <cellXfs count="258">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1719,6 +1719,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2885,25 +2888,29 @@
       <c r="AO6" s="218" t="n"/>
     </row>
     <row r="7" ht="15" customFormat="1" customHeight="1" s="34">
-      <c r="A7" s="136" t="inlineStr">
-        <is>
-          <t>BMTP</t>
-        </is>
-      </c>
-      <c r="B7" s="137" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>TIFFA</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>ICD</t>
         </is>
       </c>
       <c r="C7" s="214" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" s="215" t="n"/>
       <c r="E7" s="215" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="215" t="n"/>
-      <c r="G7" s="215" t="n"/>
+      <c r="F7" s="215" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="215" t="n">
+        <v>1</v>
+      </c>
       <c r="H7" s="215" t="n"/>
       <c r="I7" s="215" t="n"/>
       <c r="J7" s="215" t="n"/>
@@ -3097,26 +3104,38 @@
       <c r="AO9" s="224" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="41" t="n"/>
-      <c r="D10" s="28" t="n"/>
-      <c r="E10" s="28" t="n"/>
-      <c r="F10" s="28" t="n"/>
-      <c r="G10" s="28" t="n"/>
-      <c r="H10" s="28" t="n"/>
-      <c r="I10" s="28" t="n"/>
-      <c r="J10" s="28" t="n"/>
-      <c r="K10" s="42" t="n"/>
-      <c r="L10" s="35" t="n"/>
-      <c r="M10" s="29" t="n"/>
-      <c r="N10" s="29" t="n"/>
-      <c r="O10" s="29" t="n"/>
-      <c r="P10" s="29" t="n"/>
-      <c r="Q10" s="29" t="n"/>
-      <c r="R10" s="29" t="n"/>
-      <c r="S10" s="29" t="n"/>
-      <c r="T10" s="30" t="n"/>
+      <c r="A10" s="136" t="inlineStr">
+        <is>
+          <t>BMTP</t>
+        </is>
+      </c>
+      <c r="B10" s="137" t="inlineStr">
+        <is>
+          <t>ICD</t>
+        </is>
+      </c>
+      <c r="C10" s="214" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="215" t="n"/>
+      <c r="E10" s="215" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="215" t="n"/>
+      <c r="G10" s="215" t="n"/>
+      <c r="H10" s="215" t="n"/>
+      <c r="I10" s="215" t="n"/>
+      <c r="J10" s="215" t="n"/>
+      <c r="K10" s="216" t="n"/>
+      <c r="L10" s="217" t="n"/>
+      <c r="M10" s="215" t="n"/>
+      <c r="N10" s="215" t="n"/>
+      <c r="O10" s="215" t="n"/>
+      <c r="P10" s="215" t="n"/>
+      <c r="Q10" s="215" t="n"/>
+      <c r="R10" s="215" t="n"/>
+      <c r="S10" s="215" t="n"/>
+      <c r="T10" s="218" t="n"/>
       <c r="V10" s="35" t="inlineStr">
         <is>
           <t>PW</t>
@@ -3161,26 +3180,34 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="43" t="n"/>
-      <c r="B11" s="44" t="n"/>
-      <c r="C11" s="41" t="n"/>
-      <c r="D11" s="28" t="n"/>
-      <c r="E11" s="28" t="n"/>
-      <c r="F11" s="28" t="n"/>
-      <c r="G11" s="28" t="n"/>
-      <c r="H11" s="28" t="n"/>
-      <c r="I11" s="28" t="n"/>
-      <c r="J11" s="28" t="n"/>
-      <c r="K11" s="42" t="n"/>
-      <c r="L11" s="35" t="n"/>
-      <c r="M11" s="29" t="n"/>
-      <c r="N11" s="29" t="n"/>
-      <c r="O11" s="29" t="n"/>
-      <c r="P11" s="29" t="n"/>
-      <c r="Q11" s="29" t="n"/>
-      <c r="R11" s="29" t="n"/>
-      <c r="S11" s="29" t="n"/>
-      <c r="T11" s="30" t="n"/>
+      <c r="A11" s="136" t="inlineStr">
+        <is>
+          <t>SCT</t>
+        </is>
+      </c>
+      <c r="B11" s="137" t="inlineStr">
+        <is>
+          <t>ICD</t>
+        </is>
+      </c>
+      <c r="C11" s="214" t="n"/>
+      <c r="D11" s="215" t="n"/>
+      <c r="E11" s="215" t="n"/>
+      <c r="F11" s="215" t="n"/>
+      <c r="G11" s="215" t="n"/>
+      <c r="H11" s="215" t="n"/>
+      <c r="I11" s="215" t="n"/>
+      <c r="J11" s="215" t="n"/>
+      <c r="K11" s="216" t="n"/>
+      <c r="L11" s="217" t="n"/>
+      <c r="M11" s="215" t="n"/>
+      <c r="N11" s="215" t="n"/>
+      <c r="O11" s="215" t="n"/>
+      <c r="P11" s="215" t="n"/>
+      <c r="Q11" s="215" t="n"/>
+      <c r="R11" s="215" t="n"/>
+      <c r="S11" s="215" t="n"/>
+      <c r="T11" s="218" t="n"/>
       <c r="V11" s="35" t="n"/>
       <c r="W11" s="36" t="n"/>
       <c r="X11" s="39" t="n"/>
@@ -4520,26 +4547,28 @@
       <c r="AO33" s="233" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="136" t="inlineStr">
-        <is>
-          <t>BMTP</t>
-        </is>
-      </c>
-      <c r="B34" s="137" t="inlineStr">
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>TIFFA</t>
+        </is>
+      </c>
+      <c r="B34" s="44" t="inlineStr">
         <is>
           <t>ICD</t>
         </is>
       </c>
-      <c r="C34" s="234" t="n"/>
-      <c r="D34" s="235" t="n"/>
-      <c r="E34" s="235" t="n"/>
-      <c r="F34" s="235" t="n"/>
-      <c r="G34" s="235" t="n"/>
-      <c r="H34" s="235" t="n"/>
-      <c r="I34" s="235" t="n"/>
-      <c r="J34" s="235" t="n"/>
-      <c r="K34" s="236" t="n"/>
-      <c r="L34" s="231">
+      <c r="C34" s="214" t="n">
+        <v>20</v>
+      </c>
+      <c r="D34" s="215" t="n"/>
+      <c r="E34" s="215" t="n"/>
+      <c r="F34" s="215" t="n"/>
+      <c r="G34" s="215" t="n"/>
+      <c r="H34" s="215" t="n"/>
+      <c r="I34" s="215" t="n"/>
+      <c r="J34" s="215" t="n"/>
+      <c r="K34" s="216" t="n"/>
+      <c r="L34" s="237">
         <f>SUM(L7-C34)</f>
         <v/>
       </c>
@@ -4615,7 +4644,7 @@
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="C35" s="237" t="n">
+      <c r="C35" s="238" t="n">
         <v>80</v>
       </c>
       <c r="D35" s="223" t="n"/>
@@ -4627,40 +4656,40 @@
       <c r="H35" s="223" t="n"/>
       <c r="I35" s="223" t="n"/>
       <c r="J35" s="223" t="n"/>
-      <c r="K35" s="238" t="n"/>
-      <c r="L35" s="239">
+      <c r="K35" s="239" t="n"/>
+      <c r="L35" s="240">
         <f>SUM(L8-C35)</f>
         <v/>
       </c>
-      <c r="M35" s="240">
+      <c r="M35" s="241">
         <f>SUM(M8-D35)</f>
         <v/>
       </c>
-      <c r="N35" s="240">
+      <c r="N35" s="241">
         <f>SUM(N8-E35)</f>
         <v/>
       </c>
-      <c r="O35" s="240">
+      <c r="O35" s="241">
         <f>SUM(O8-F35)</f>
         <v/>
       </c>
-      <c r="P35" s="240">
+      <c r="P35" s="241">
         <f>SUM(P8-G35)</f>
         <v/>
       </c>
-      <c r="Q35" s="240">
+      <c r="Q35" s="241">
         <f>SUM(Q8-H35)</f>
         <v/>
       </c>
-      <c r="R35" s="240">
+      <c r="R35" s="241">
         <f>SUM(R8-I35)</f>
         <v/>
       </c>
-      <c r="S35" s="240">
+      <c r="S35" s="241">
         <f>SUM(S8-J35)</f>
         <v/>
       </c>
-      <c r="T35" s="241">
+      <c r="T35" s="242">
         <f>SUM(T8-K35)</f>
         <v/>
       </c>
@@ -4674,7 +4703,7 @@
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="X35" s="237" t="n">
+      <c r="X35" s="238" t="n">
         <v>108</v>
       </c>
       <c r="Y35" s="223" t="n"/>
@@ -4690,40 +4719,40 @@
       <c r="AC35" s="223" t="n"/>
       <c r="AD35" s="223" t="n"/>
       <c r="AE35" s="223" t="n"/>
-      <c r="AF35" s="238" t="n"/>
-      <c r="AG35" s="239">
+      <c r="AF35" s="239" t="n"/>
+      <c r="AG35" s="240">
         <f>SUM(AG8-X35)</f>
         <v/>
       </c>
-      <c r="AH35" s="240">
+      <c r="AH35" s="241">
         <f>SUM(AH8-Y35)</f>
         <v/>
       </c>
-      <c r="AI35" s="240">
+      <c r="AI35" s="241">
         <f>SUM(AI8-Z35)</f>
         <v/>
       </c>
-      <c r="AJ35" s="240">
+      <c r="AJ35" s="241">
         <f>SUM(AJ8-AA35)</f>
         <v/>
       </c>
-      <c r="AK35" s="240">
+      <c r="AK35" s="241">
         <f>SUM(AK8-AB35)</f>
         <v/>
       </c>
-      <c r="AL35" s="240">
+      <c r="AL35" s="241">
         <f>SUM(AL8-AC35)</f>
         <v/>
       </c>
-      <c r="AM35" s="240">
+      <c r="AM35" s="241">
         <f>SUM(AM8-AD35)</f>
         <v/>
       </c>
-      <c r="AN35" s="240">
+      <c r="AN35" s="241">
         <f>SUM(AN8-AE35)</f>
         <v/>
       </c>
-      <c r="AO35" s="241">
+      <c r="AO35" s="242">
         <f>SUM(AO8-AF35)</f>
         <v/>
       </c>
@@ -4739,7 +4768,7 @@
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="C36" s="237" t="n">
+      <c r="C36" s="238" t="n">
         <v>250</v>
       </c>
       <c r="D36" s="223" t="n"/>
@@ -4755,40 +4784,40 @@
       <c r="H36" s="223" t="n"/>
       <c r="I36" s="223" t="n"/>
       <c r="J36" s="223" t="n"/>
-      <c r="K36" s="238" t="n"/>
-      <c r="L36" s="239">
+      <c r="K36" s="239" t="n"/>
+      <c r="L36" s="240">
         <f>SUM(L9-C36)</f>
         <v/>
       </c>
-      <c r="M36" s="240">
+      <c r="M36" s="241">
         <f>SUM(M9-D36)</f>
         <v/>
       </c>
-      <c r="N36" s="240">
+      <c r="N36" s="241">
         <f>SUM(N9-E36)</f>
         <v/>
       </c>
-      <c r="O36" s="240">
+      <c r="O36" s="241">
         <f>SUM(O9-F36)</f>
         <v/>
       </c>
-      <c r="P36" s="240">
+      <c r="P36" s="241">
         <f>SUM(P9-G36)</f>
         <v/>
       </c>
-      <c r="Q36" s="240">
+      <c r="Q36" s="241">
         <f>SUM(Q9-H36)</f>
         <v/>
       </c>
-      <c r="R36" s="240">
+      <c r="R36" s="241">
         <f>SUM(R9-I36)</f>
         <v/>
       </c>
-      <c r="S36" s="240">
+      <c r="S36" s="241">
         <f>SUM(S9-J36)</f>
         <v/>
       </c>
-      <c r="T36" s="241">
+      <c r="T36" s="242">
         <f>SUM(T9-K36)</f>
         <v/>
       </c>
@@ -4802,7 +4831,7 @@
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="X36" s="237" t="n">
+      <c r="X36" s="238" t="n">
         <v>5</v>
       </c>
       <c r="Y36" s="223" t="n"/>
@@ -4814,89 +4843,97 @@
       <c r="AC36" s="223" t="n"/>
       <c r="AD36" s="223" t="n"/>
       <c r="AE36" s="223" t="n"/>
-      <c r="AF36" s="238" t="n"/>
-      <c r="AG36" s="239">
+      <c r="AF36" s="239" t="n"/>
+      <c r="AG36" s="240">
         <f>SUM(AG9-X36)</f>
         <v/>
       </c>
-      <c r="AH36" s="240">
+      <c r="AH36" s="241">
         <f>SUM(AH9-Y36)</f>
         <v/>
       </c>
-      <c r="AI36" s="240">
+      <c r="AI36" s="241">
         <f>SUM(AI9-Z36)</f>
         <v/>
       </c>
-      <c r="AJ36" s="240">
+      <c r="AJ36" s="241">
         <f>SUM(AJ9-AA36)</f>
         <v/>
       </c>
-      <c r="AK36" s="240">
+      <c r="AK36" s="241">
         <f>SUM(AK9-AB36)</f>
         <v/>
       </c>
-      <c r="AL36" s="240">
+      <c r="AL36" s="241">
         <f>SUM(AL9-AC36)</f>
         <v/>
       </c>
-      <c r="AM36" s="240">
+      <c r="AM36" s="241">
         <f>SUM(AM9-AD36)</f>
         <v/>
       </c>
-      <c r="AN36" s="240">
+      <c r="AN36" s="241">
         <f>SUM(AN9-AE36)</f>
         <v/>
       </c>
-      <c r="AO36" s="241">
+      <c r="AO36" s="242">
         <f>SUM(AO9-AF36)</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="43" t="n"/>
-      <c r="B37" s="44" t="n"/>
-      <c r="C37" s="48" t="n"/>
-      <c r="D37" s="49" t="n"/>
-      <c r="E37" s="49" t="n"/>
-      <c r="F37" s="49" t="n"/>
-      <c r="G37" s="49" t="n"/>
-      <c r="H37" s="49" t="n"/>
-      <c r="I37" s="49" t="n"/>
-      <c r="J37" s="49" t="n"/>
-      <c r="K37" s="82" t="n"/>
-      <c r="L37" s="242">
+      <c r="A37" s="136" t="inlineStr">
+        <is>
+          <t>BMTP</t>
+        </is>
+      </c>
+      <c r="B37" s="137" t="inlineStr">
+        <is>
+          <t>ICD</t>
+        </is>
+      </c>
+      <c r="C37" s="234" t="n"/>
+      <c r="D37" s="235" t="n"/>
+      <c r="E37" s="235" t="n"/>
+      <c r="F37" s="235" t="n"/>
+      <c r="G37" s="235" t="n"/>
+      <c r="H37" s="235" t="n"/>
+      <c r="I37" s="235" t="n"/>
+      <c r="J37" s="235" t="n"/>
+      <c r="K37" s="236" t="n"/>
+      <c r="L37" s="231">
         <f>SUM(L10-C37)</f>
         <v/>
       </c>
-      <c r="M37" s="243">
+      <c r="M37" s="232">
         <f>SUM(M10-D37)</f>
         <v/>
       </c>
-      <c r="N37" s="243">
+      <c r="N37" s="232">
         <f>SUM(N10-E37)</f>
         <v/>
       </c>
-      <c r="O37" s="243">
+      <c r="O37" s="232">
         <f>SUM(O10-F37)</f>
         <v/>
       </c>
-      <c r="P37" s="243">
+      <c r="P37" s="232">
         <f>SUM(P10-G37)</f>
         <v/>
       </c>
-      <c r="Q37" s="243">
+      <c r="Q37" s="232">
         <f>SUM(Q10-H37)</f>
         <v/>
       </c>
-      <c r="R37" s="243">
+      <c r="R37" s="232">
         <f>SUM(R10-I37)</f>
         <v/>
       </c>
-      <c r="S37" s="243">
+      <c r="S37" s="232">
         <f>SUM(S10-J37)</f>
         <v/>
       </c>
-      <c r="T37" s="244">
+      <c r="T37" s="233">
         <f>SUM(T10-K37)</f>
         <v/>
       </c>
@@ -4910,7 +4947,7 @@
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="X37" s="237" t="n">
+      <c r="X37" s="238" t="n">
         <v>390</v>
       </c>
       <c r="Y37" s="223" t="n">
@@ -4926,89 +4963,97 @@
       </c>
       <c r="AD37" s="223" t="n"/>
       <c r="AE37" s="223" t="n"/>
-      <c r="AF37" s="238" t="n"/>
-      <c r="AG37" s="239">
+      <c r="AF37" s="239" t="n"/>
+      <c r="AG37" s="240">
         <f>SUM(AG10-X37)</f>
         <v/>
       </c>
-      <c r="AH37" s="240">
+      <c r="AH37" s="241">
         <f>SUM(AH10-Y37)</f>
         <v/>
       </c>
-      <c r="AI37" s="240">
+      <c r="AI37" s="241">
         <f>SUM(AI10-Z37)</f>
         <v/>
       </c>
-      <c r="AJ37" s="240">
+      <c r="AJ37" s="241">
         <f>SUM(AJ10-AA37)</f>
         <v/>
       </c>
-      <c r="AK37" s="240">
+      <c r="AK37" s="241">
         <f>SUM(AK10-AB37)</f>
         <v/>
       </c>
-      <c r="AL37" s="240">
+      <c r="AL37" s="241">
         <f>SUM(AL10-AC37)</f>
         <v/>
       </c>
-      <c r="AM37" s="240">
+      <c r="AM37" s="241">
         <f>SUM(AM10-AD37)</f>
         <v/>
       </c>
-      <c r="AN37" s="240">
+      <c r="AN37" s="241">
         <f>SUM(AN10-AE37)</f>
         <v/>
       </c>
-      <c r="AO37" s="241">
+      <c r="AO37" s="242">
         <f>SUM(AO10-AF37)</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="43" t="n"/>
-      <c r="B38" s="44" t="n"/>
-      <c r="C38" s="48" t="n"/>
-      <c r="D38" s="49" t="n"/>
-      <c r="E38" s="49" t="n"/>
-      <c r="F38" s="49" t="n"/>
-      <c r="G38" s="49" t="n"/>
-      <c r="H38" s="49" t="n"/>
-      <c r="I38" s="49" t="n"/>
-      <c r="J38" s="49" t="n"/>
-      <c r="K38" s="82" t="n"/>
-      <c r="L38" s="242">
+      <c r="A38" s="136" t="inlineStr">
+        <is>
+          <t>SCT</t>
+        </is>
+      </c>
+      <c r="B38" s="137" t="inlineStr">
+        <is>
+          <t>ICD</t>
+        </is>
+      </c>
+      <c r="C38" s="234" t="n"/>
+      <c r="D38" s="235" t="n"/>
+      <c r="E38" s="235" t="n"/>
+      <c r="F38" s="235" t="n"/>
+      <c r="G38" s="235" t="n"/>
+      <c r="H38" s="235" t="n"/>
+      <c r="I38" s="235" t="n"/>
+      <c r="J38" s="235" t="n"/>
+      <c r="K38" s="236" t="n"/>
+      <c r="L38" s="231">
         <f>SUM(L11-C38)</f>
         <v/>
       </c>
-      <c r="M38" s="243">
+      <c r="M38" s="232">
         <f>SUM(M11-D38)</f>
         <v/>
       </c>
-      <c r="N38" s="243">
+      <c r="N38" s="232">
         <f>SUM(N11-E38)</f>
         <v/>
       </c>
-      <c r="O38" s="243">
+      <c r="O38" s="232">
         <f>SUM(O11-F38)</f>
         <v/>
       </c>
-      <c r="P38" s="243">
+      <c r="P38" s="232">
         <f>SUM(P11-G38)</f>
         <v/>
       </c>
-      <c r="Q38" s="243">
+      <c r="Q38" s="232">
         <f>SUM(Q11-H38)</f>
         <v/>
       </c>
-      <c r="R38" s="243">
+      <c r="R38" s="232">
         <f>SUM(R11-I38)</f>
         <v/>
       </c>
-      <c r="S38" s="243">
+      <c r="S38" s="232">
         <f>SUM(S11-J38)</f>
         <v/>
       </c>
-      <c r="T38" s="244">
+      <c r="T38" s="233">
         <f>SUM(T11-K38)</f>
         <v/>
       </c>
@@ -5023,39 +5068,39 @@
       <c r="AD38" s="49" t="n"/>
       <c r="AE38" s="49" t="n"/>
       <c r="AF38" s="82" t="n"/>
-      <c r="AG38" s="242">
+      <c r="AG38" s="243">
         <f>SUM(AG11-X38)</f>
         <v/>
       </c>
-      <c r="AH38" s="243">
+      <c r="AH38" s="244">
         <f>SUM(AH11-Y38)</f>
         <v/>
       </c>
-      <c r="AI38" s="243">
+      <c r="AI38" s="244">
         <f>SUM(AI11-Z38)</f>
         <v/>
       </c>
-      <c r="AJ38" s="243">
+      <c r="AJ38" s="244">
         <f>SUM(AJ11-AA38)</f>
         <v/>
       </c>
-      <c r="AK38" s="243">
+      <c r="AK38" s="244">
         <f>SUM(AK11-AB38)</f>
         <v/>
       </c>
-      <c r="AL38" s="243">
+      <c r="AL38" s="244">
         <f>SUM(AL11-AC38)</f>
         <v/>
       </c>
-      <c r="AM38" s="243">
+      <c r="AM38" s="244">
         <f>SUM(AM11-AD38)</f>
         <v/>
       </c>
-      <c r="AN38" s="243">
+      <c r="AN38" s="244">
         <f>SUM(AN11-AE38)</f>
         <v/>
       </c>
-      <c r="AO38" s="244">
+      <c r="AO38" s="245">
         <f>SUM(AO11-AF38)</f>
         <v/>
       </c>
@@ -5072,39 +5117,39 @@
       <c r="I39" s="49" t="n"/>
       <c r="J39" s="49" t="n"/>
       <c r="K39" s="82" t="n"/>
-      <c r="L39" s="242">
+      <c r="L39" s="243">
         <f>SUM(L12-C39)</f>
         <v/>
       </c>
-      <c r="M39" s="243">
+      <c r="M39" s="244">
         <f>SUM(M12-D39)</f>
         <v/>
       </c>
-      <c r="N39" s="243">
+      <c r="N39" s="244">
         <f>SUM(N12-E39)</f>
         <v/>
       </c>
-      <c r="O39" s="243">
+      <c r="O39" s="244">
         <f>SUM(O12-F39)</f>
         <v/>
       </c>
-      <c r="P39" s="243">
+      <c r="P39" s="244">
         <f>SUM(P12-G39)</f>
         <v/>
       </c>
-      <c r="Q39" s="243">
+      <c r="Q39" s="244">
         <f>SUM(Q12-H39)</f>
         <v/>
       </c>
-      <c r="R39" s="243">
+      <c r="R39" s="244">
         <f>SUM(R12-I39)</f>
         <v/>
       </c>
-      <c r="S39" s="243">
+      <c r="S39" s="244">
         <f>SUM(S12-J39)</f>
         <v/>
       </c>
-      <c r="T39" s="244">
+      <c r="T39" s="245">
         <f>SUM(T12-K39)</f>
         <v/>
       </c>
@@ -5119,39 +5164,39 @@
       <c r="AD39" s="49" t="n"/>
       <c r="AE39" s="49" t="n"/>
       <c r="AF39" s="82" t="n"/>
-      <c r="AG39" s="242">
+      <c r="AG39" s="243">
         <f>SUM(AG12-X39)</f>
         <v/>
       </c>
-      <c r="AH39" s="243">
+      <c r="AH39" s="244">
         <f>SUM(AH12-Y39)</f>
         <v/>
       </c>
-      <c r="AI39" s="243">
+      <c r="AI39" s="244">
         <f>SUM(AI12-Z39)</f>
         <v/>
       </c>
-      <c r="AJ39" s="243">
+      <c r="AJ39" s="244">
         <f>SUM(AJ12-AA39)</f>
         <v/>
       </c>
-      <c r="AK39" s="243">
+      <c r="AK39" s="244">
         <f>SUM(AK12-AB39)</f>
         <v/>
       </c>
-      <c r="AL39" s="243">
+      <c r="AL39" s="244">
         <f>SUM(AL12-AC39)</f>
         <v/>
       </c>
-      <c r="AM39" s="243">
+      <c r="AM39" s="244">
         <f>SUM(AM12-AD39)</f>
         <v/>
       </c>
-      <c r="AN39" s="243">
+      <c r="AN39" s="244">
         <f>SUM(AN12-AE39)</f>
         <v/>
       </c>
-      <c r="AO39" s="244">
+      <c r="AO39" s="245">
         <f>SUM(AO12-AF39)</f>
         <v/>
       </c>
@@ -5177,39 +5222,39 @@
       <c r="I40" s="85" t="n"/>
       <c r="J40" s="85" t="n"/>
       <c r="K40" s="86" t="n"/>
-      <c r="L40" s="245">
+      <c r="L40" s="246">
         <f>SUM(L13-C40)</f>
         <v/>
       </c>
-      <c r="M40" s="246">
+      <c r="M40" s="247">
         <f>SUM(M13-D40)</f>
         <v/>
       </c>
-      <c r="N40" s="246">
+      <c r="N40" s="247">
         <f>SUM(N13-E40)</f>
         <v/>
       </c>
-      <c r="O40" s="246">
+      <c r="O40" s="247">
         <f>SUM(O13-F40)</f>
         <v/>
       </c>
-      <c r="P40" s="246">
+      <c r="P40" s="247">
         <f>SUM(P13-G40)</f>
         <v/>
       </c>
-      <c r="Q40" s="246">
+      <c r="Q40" s="247">
         <f>SUM(Q13-H40)</f>
         <v/>
       </c>
-      <c r="R40" s="246">
+      <c r="R40" s="247">
         <f>SUM(R13-I40)</f>
         <v/>
       </c>
-      <c r="S40" s="246">
+      <c r="S40" s="247">
         <f>SUM(S13-J40)</f>
         <v/>
       </c>
-      <c r="T40" s="247">
+      <c r="T40" s="248">
         <f>SUM(T13-K40)</f>
         <v/>
       </c>
@@ -5228,39 +5273,39 @@
       <c r="AD40" s="85" t="n"/>
       <c r="AE40" s="85" t="n"/>
       <c r="AF40" s="86" t="n"/>
-      <c r="AG40" s="242">
+      <c r="AG40" s="243">
         <f>SUM(AG13-X40)</f>
         <v/>
       </c>
-      <c r="AH40" s="243">
+      <c r="AH40" s="244">
         <f>SUM(AH13-Y40)</f>
         <v/>
       </c>
-      <c r="AI40" s="243">
+      <c r="AI40" s="244">
         <f>SUM(AI13-Z40)</f>
         <v/>
       </c>
-      <c r="AJ40" s="243">
+      <c r="AJ40" s="244">
         <f>SUM(AJ13-AA40)</f>
         <v/>
       </c>
-      <c r="AK40" s="243">
+      <c r="AK40" s="244">
         <f>SUM(AK13-AB40)</f>
         <v/>
       </c>
-      <c r="AL40" s="243">
+      <c r="AL40" s="244">
         <f>SUM(AL13-AC40)</f>
         <v/>
       </c>
-      <c r="AM40" s="243">
+      <c r="AM40" s="244">
         <f>SUM(AM13-AD40)</f>
         <v/>
       </c>
-      <c r="AN40" s="243">
+      <c r="AN40" s="244">
         <f>SUM(AN13-AE40)</f>
         <v/>
       </c>
-      <c r="AO40" s="244">
+      <c r="AO40" s="245">
         <f>SUM(AO13-AF40)</f>
         <v/>
       </c>
@@ -5710,7 +5755,7 @@
       <c r="I45" s="207" t="n"/>
       <c r="J45" s="207" t="n"/>
       <c r="K45" s="208" t="n"/>
-      <c r="L45" s="248">
+      <c r="L45" s="249">
         <f>SUM(L31-C45)</f>
         <v/>
       </c>
@@ -5718,7 +5763,7 @@
         <f>SUM(M31-D45)</f>
         <v/>
       </c>
-      <c r="N45" s="249">
+      <c r="N45" s="250">
         <f>SUM(N31-E45)</f>
         <v/>
       </c>
@@ -5946,26 +5991,28 @@
       <c r="AO47" s="233" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="136" t="inlineStr">
-        <is>
-          <t>BMTP</t>
-        </is>
-      </c>
-      <c r="B48" s="137" t="inlineStr">
+      <c r="A48" s="23" t="inlineStr">
+        <is>
+          <t>TIFFA</t>
+        </is>
+      </c>
+      <c r="B48" s="44" t="inlineStr">
         <is>
           <t>ICD</t>
         </is>
       </c>
-      <c r="C48" s="234" t="n"/>
-      <c r="D48" s="235" t="n"/>
-      <c r="E48" s="235" t="n"/>
-      <c r="F48" s="235" t="n"/>
-      <c r="G48" s="235" t="n"/>
-      <c r="H48" s="235" t="n"/>
-      <c r="I48" s="235" t="n"/>
-      <c r="J48" s="235" t="n"/>
-      <c r="K48" s="236" t="n"/>
-      <c r="L48" s="231">
+      <c r="C48" s="214" t="n">
+        <v>20</v>
+      </c>
+      <c r="D48" s="215" t="n"/>
+      <c r="E48" s="215" t="n"/>
+      <c r="F48" s="215" t="n"/>
+      <c r="G48" s="215" t="n"/>
+      <c r="H48" s="215" t="n"/>
+      <c r="I48" s="215" t="n"/>
+      <c r="J48" s="215" t="n"/>
+      <c r="K48" s="216" t="n"/>
+      <c r="L48" s="237">
         <f>SUM(L34-C48)</f>
         <v/>
       </c>
@@ -6041,7 +6088,7 @@
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="C49" s="237" t="n">
+      <c r="C49" s="238" t="n">
         <v>20</v>
       </c>
       <c r="D49" s="223" t="n"/>
@@ -6053,40 +6100,40 @@
       <c r="H49" s="223" t="n"/>
       <c r="I49" s="223" t="n"/>
       <c r="J49" s="223" t="n"/>
-      <c r="K49" s="238" t="n"/>
-      <c r="L49" s="239">
+      <c r="K49" s="239" t="n"/>
+      <c r="L49" s="240">
         <f>SUM(L35-C49)</f>
         <v/>
       </c>
-      <c r="M49" s="240">
+      <c r="M49" s="241">
         <f>SUM(M35-D49)</f>
         <v/>
       </c>
-      <c r="N49" s="240">
+      <c r="N49" s="241">
         <f>SUM(N35-E49)</f>
         <v/>
       </c>
-      <c r="O49" s="240">
+      <c r="O49" s="241">
         <f>SUM(O35-F49)</f>
         <v/>
       </c>
-      <c r="P49" s="240">
+      <c r="P49" s="241">
         <f>SUM(P35-G49)</f>
         <v/>
       </c>
-      <c r="Q49" s="240">
+      <c r="Q49" s="241">
         <f>SUM(Q35-H49)</f>
         <v/>
       </c>
-      <c r="R49" s="240">
+      <c r="R49" s="241">
         <f>SUM(R35-I49)</f>
         <v/>
       </c>
-      <c r="S49" s="240">
+      <c r="S49" s="241">
         <f>SUM(S35-J49)</f>
         <v/>
       </c>
-      <c r="T49" s="241">
+      <c r="T49" s="242">
         <f>SUM(T35-K49)</f>
         <v/>
       </c>
@@ -6100,7 +6147,7 @@
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="X49" s="237" t="n">
+      <c r="X49" s="238" t="n">
         <v>88</v>
       </c>
       <c r="Y49" s="223" t="n"/>
@@ -6116,40 +6163,40 @@
       <c r="AC49" s="223" t="n"/>
       <c r="AD49" s="223" t="n"/>
       <c r="AE49" s="223" t="n"/>
-      <c r="AF49" s="238" t="n"/>
-      <c r="AG49" s="239">
+      <c r="AF49" s="239" t="n"/>
+      <c r="AG49" s="240">
         <f>SUM(AG35-X49)</f>
         <v/>
       </c>
-      <c r="AH49" s="240">
+      <c r="AH49" s="241">
         <f>SUM(AH35-Y49)</f>
         <v/>
       </c>
-      <c r="AI49" s="240">
+      <c r="AI49" s="241">
         <f>SUM(AI35-Z49)</f>
         <v/>
       </c>
-      <c r="AJ49" s="240">
+      <c r="AJ49" s="241">
         <f>SUM(AJ35-AA49)</f>
         <v/>
       </c>
-      <c r="AK49" s="240">
+      <c r="AK49" s="241">
         <f>SUM(AK35-AB49)</f>
         <v/>
       </c>
-      <c r="AL49" s="240">
+      <c r="AL49" s="241">
         <f>SUM(AL35-AC49)</f>
         <v/>
       </c>
-      <c r="AM49" s="240">
+      <c r="AM49" s="241">
         <f>SUM(AM35-AD49)</f>
         <v/>
       </c>
-      <c r="AN49" s="240">
+      <c r="AN49" s="241">
         <f>SUM(AN35-AE49)</f>
         <v/>
       </c>
-      <c r="AO49" s="241">
+      <c r="AO49" s="242">
         <f>SUM(AO35-AF49)</f>
         <v/>
       </c>
@@ -6165,7 +6212,7 @@
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="C50" s="237" t="n">
+      <c r="C50" s="238" t="n">
         <v>207</v>
       </c>
       <c r="D50" s="223" t="n">
@@ -6183,40 +6230,40 @@
       <c r="H50" s="223" t="n"/>
       <c r="I50" s="223" t="n"/>
       <c r="J50" s="223" t="n"/>
-      <c r="K50" s="238" t="n"/>
-      <c r="L50" s="239">
+      <c r="K50" s="239" t="n"/>
+      <c r="L50" s="240">
         <f>SUM(L36-C50)</f>
         <v/>
       </c>
-      <c r="M50" s="240">
+      <c r="M50" s="241">
         <f>SUM(M36-D50)</f>
         <v/>
       </c>
-      <c r="N50" s="240">
+      <c r="N50" s="241">
         <f>SUM(N36-E50)</f>
         <v/>
       </c>
-      <c r="O50" s="240">
+      <c r="O50" s="241">
         <f>SUM(O36-F50)</f>
         <v/>
       </c>
-      <c r="P50" s="250">
+      <c r="P50" s="251">
         <f>SUM(P36-G50)</f>
         <v/>
       </c>
-      <c r="Q50" s="240">
+      <c r="Q50" s="241">
         <f>SUM(Q36-H50)</f>
         <v/>
       </c>
-      <c r="R50" s="240">
+      <c r="R50" s="241">
         <f>SUM(R36-I50)</f>
         <v/>
       </c>
-      <c r="S50" s="240">
+      <c r="S50" s="241">
         <f>SUM(S36-J50)</f>
         <v/>
       </c>
-      <c r="T50" s="241">
+      <c r="T50" s="242">
         <f>SUM(T36-K50)</f>
         <v/>
       </c>
@@ -6230,7 +6277,7 @@
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="X50" s="237" t="n"/>
+      <c r="X50" s="238" t="n"/>
       <c r="Y50" s="223" t="n"/>
       <c r="Z50" s="223" t="n">
         <v>1</v>
@@ -6240,89 +6287,97 @@
       <c r="AC50" s="223" t="n"/>
       <c r="AD50" s="223" t="n"/>
       <c r="AE50" s="223" t="n"/>
-      <c r="AF50" s="238" t="n"/>
-      <c r="AG50" s="239">
+      <c r="AF50" s="239" t="n"/>
+      <c r="AG50" s="240">
         <f>SUM(AG36-X50)</f>
         <v/>
       </c>
-      <c r="AH50" s="240">
+      <c r="AH50" s="241">
         <f>SUM(AH36-Y50)</f>
         <v/>
       </c>
-      <c r="AI50" s="240">
+      <c r="AI50" s="241">
         <f>SUM(AI36-Z50)</f>
         <v/>
       </c>
-      <c r="AJ50" s="240">
+      <c r="AJ50" s="241">
         <f>SUM(AJ36-AA50)</f>
         <v/>
       </c>
-      <c r="AK50" s="240">
+      <c r="AK50" s="241">
         <f>SUM(AK36-AB50)</f>
         <v/>
       </c>
-      <c r="AL50" s="240">
+      <c r="AL50" s="241">
         <f>SUM(AL36-AC50)</f>
         <v/>
       </c>
-      <c r="AM50" s="240">
+      <c r="AM50" s="241">
         <f>SUM(AM36-AD50)</f>
         <v/>
       </c>
-      <c r="AN50" s="240">
+      <c r="AN50" s="241">
         <f>SUM(AN36-AE50)</f>
         <v/>
       </c>
-      <c r="AO50" s="241">
+      <c r="AO50" s="242">
         <f>SUM(AO36-AF50)</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="43" t="n"/>
-      <c r="B51" s="44" t="n"/>
-      <c r="C51" s="41" t="n"/>
-      <c r="D51" s="28" t="n"/>
-      <c r="E51" s="28" t="n"/>
-      <c r="F51" s="28" t="n"/>
-      <c r="G51" s="28" t="n"/>
-      <c r="H51" s="28" t="n"/>
-      <c r="I51" s="28" t="n"/>
-      <c r="J51" s="28" t="n"/>
-      <c r="K51" s="42" t="n"/>
-      <c r="L51" s="242">
+      <c r="A51" s="136" t="inlineStr">
+        <is>
+          <t>BMTP</t>
+        </is>
+      </c>
+      <c r="B51" s="137" t="inlineStr">
+        <is>
+          <t>ICD</t>
+        </is>
+      </c>
+      <c r="C51" s="234" t="n"/>
+      <c r="D51" s="235" t="n"/>
+      <c r="E51" s="235" t="n"/>
+      <c r="F51" s="235" t="n"/>
+      <c r="G51" s="235" t="n"/>
+      <c r="H51" s="235" t="n"/>
+      <c r="I51" s="235" t="n"/>
+      <c r="J51" s="235" t="n"/>
+      <c r="K51" s="236" t="n"/>
+      <c r="L51" s="231">
         <f>SUM(L37-C51)</f>
         <v/>
       </c>
-      <c r="M51" s="243">
+      <c r="M51" s="232">
         <f>SUM(M37-D51)</f>
         <v/>
       </c>
-      <c r="N51" s="243">
+      <c r="N51" s="232">
         <f>SUM(N37-E51)</f>
         <v/>
       </c>
-      <c r="O51" s="243">
+      <c r="O51" s="232">
         <f>SUM(O37-F51)</f>
         <v/>
       </c>
-      <c r="P51" s="243">
+      <c r="P51" s="232">
         <f>SUM(P37-G51)</f>
         <v/>
       </c>
-      <c r="Q51" s="243">
+      <c r="Q51" s="232">
         <f>SUM(Q37-H51)</f>
         <v/>
       </c>
-      <c r="R51" s="243">
+      <c r="R51" s="232">
         <f>SUM(R37-I51)</f>
         <v/>
       </c>
-      <c r="S51" s="243">
+      <c r="S51" s="232">
         <f>SUM(S37-J51)</f>
         <v/>
       </c>
-      <c r="T51" s="244">
+      <c r="T51" s="233">
         <f>SUM(T37-K51)</f>
         <v/>
       </c>
@@ -6336,7 +6391,7 @@
           <t>DEPOT</t>
         </is>
       </c>
-      <c r="X51" s="237" t="n">
+      <c r="X51" s="238" t="n">
         <v>155</v>
       </c>
       <c r="Y51" s="223" t="n"/>
@@ -6348,89 +6403,97 @@
       <c r="AC51" s="223" t="n"/>
       <c r="AD51" s="223" t="n"/>
       <c r="AE51" s="223" t="n"/>
-      <c r="AF51" s="238" t="n"/>
-      <c r="AG51" s="239">
+      <c r="AF51" s="239" t="n"/>
+      <c r="AG51" s="240">
         <f>SUM(AG37-X51)</f>
         <v/>
       </c>
-      <c r="AH51" s="240">
+      <c r="AH51" s="241">
         <f>SUM(AH37-Y51)</f>
         <v/>
       </c>
-      <c r="AI51" s="240">
+      <c r="AI51" s="241">
         <f>SUM(AI37-Z51)</f>
         <v/>
       </c>
-      <c r="AJ51" s="240">
+      <c r="AJ51" s="241">
         <f>SUM(AJ37-AA51)</f>
         <v/>
       </c>
-      <c r="AK51" s="240">
+      <c r="AK51" s="241">
         <f>SUM(AK37-AB51)</f>
         <v/>
       </c>
-      <c r="AL51" s="240">
+      <c r="AL51" s="241">
         <f>SUM(AL37-AC51)</f>
         <v/>
       </c>
-      <c r="AM51" s="240">
+      <c r="AM51" s="241">
         <f>SUM(AM37-AD51)</f>
         <v/>
       </c>
-      <c r="AN51" s="240">
+      <c r="AN51" s="241">
         <f>SUM(AN37-AE51)</f>
         <v/>
       </c>
-      <c r="AO51" s="241">
+      <c r="AO51" s="242">
         <f>SUM(AO37-AF51)</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="43" t="n"/>
-      <c r="B52" s="44" t="n"/>
-      <c r="C52" s="41" t="n"/>
-      <c r="D52" s="28" t="n"/>
-      <c r="E52" s="28" t="n"/>
-      <c r="F52" s="28" t="n"/>
-      <c r="G52" s="28" t="n"/>
-      <c r="H52" s="28" t="n"/>
-      <c r="I52" s="28" t="n"/>
-      <c r="J52" s="28" t="n"/>
-      <c r="K52" s="42" t="n"/>
-      <c r="L52" s="242">
+      <c r="A52" s="136" t="inlineStr">
+        <is>
+          <t>SCT</t>
+        </is>
+      </c>
+      <c r="B52" s="137" t="inlineStr">
+        <is>
+          <t>ICD</t>
+        </is>
+      </c>
+      <c r="C52" s="234" t="n"/>
+      <c r="D52" s="235" t="n"/>
+      <c r="E52" s="235" t="n"/>
+      <c r="F52" s="235" t="n"/>
+      <c r="G52" s="235" t="n"/>
+      <c r="H52" s="235" t="n"/>
+      <c r="I52" s="235" t="n"/>
+      <c r="J52" s="235" t="n"/>
+      <c r="K52" s="236" t="n"/>
+      <c r="L52" s="231">
         <f>SUM(L38-C52)</f>
         <v/>
       </c>
-      <c r="M52" s="243">
+      <c r="M52" s="232">
         <f>SUM(M38-D52)</f>
         <v/>
       </c>
-      <c r="N52" s="243">
+      <c r="N52" s="232">
         <f>SUM(N38-E52)</f>
         <v/>
       </c>
-      <c r="O52" s="243">
+      <c r="O52" s="232">
         <f>SUM(O38-F52)</f>
         <v/>
       </c>
-      <c r="P52" s="243">
+      <c r="P52" s="232">
         <f>SUM(P38-G52)</f>
         <v/>
       </c>
-      <c r="Q52" s="243">
+      <c r="Q52" s="232">
         <f>SUM(Q38-H52)</f>
         <v/>
       </c>
-      <c r="R52" s="243">
+      <c r="R52" s="232">
         <f>SUM(R38-I52)</f>
         <v/>
       </c>
-      <c r="S52" s="243">
+      <c r="S52" s="232">
         <f>SUM(S38-J52)</f>
         <v/>
       </c>
-      <c r="T52" s="244">
+      <c r="T52" s="233">
         <f>SUM(T38-K52)</f>
         <v/>
       </c>
@@ -6445,39 +6508,39 @@
       <c r="AD52" s="49" t="n"/>
       <c r="AE52" s="49" t="n"/>
       <c r="AF52" s="82" t="n"/>
-      <c r="AG52" s="242">
+      <c r="AG52" s="243">
         <f>SUM(AG38-X52)</f>
         <v/>
       </c>
-      <c r="AH52" s="243">
+      <c r="AH52" s="244">
         <f>SUM(AH38-Y52)</f>
         <v/>
       </c>
-      <c r="AI52" s="243">
+      <c r="AI52" s="244">
         <f>SUM(AI38-Z52)</f>
         <v/>
       </c>
-      <c r="AJ52" s="243">
+      <c r="AJ52" s="244">
         <f>SUM(AJ38-AA52)</f>
         <v/>
       </c>
-      <c r="AK52" s="243">
+      <c r="AK52" s="244">
         <f>SUM(AK38-AB52)</f>
         <v/>
       </c>
-      <c r="AL52" s="243">
+      <c r="AL52" s="244">
         <f>SUM(AL38-AC52)</f>
         <v/>
       </c>
-      <c r="AM52" s="243">
+      <c r="AM52" s="244">
         <f>SUM(AM38-AD52)</f>
         <v/>
       </c>
-      <c r="AN52" s="243">
+      <c r="AN52" s="244">
         <f>SUM(AN38-AE52)</f>
         <v/>
       </c>
-      <c r="AO52" s="244">
+      <c r="AO52" s="245">
         <f>SUM(AO38-AF52)</f>
         <v/>
       </c>
@@ -6494,39 +6557,39 @@
       <c r="I53" s="28" t="n"/>
       <c r="J53" s="28" t="n"/>
       <c r="K53" s="42" t="n"/>
-      <c r="L53" s="242">
+      <c r="L53" s="243">
         <f>SUM(L39-C53)</f>
         <v/>
       </c>
-      <c r="M53" s="243">
+      <c r="M53" s="244">
         <f>SUM(M39-D53)</f>
         <v/>
       </c>
-      <c r="N53" s="243">
+      <c r="N53" s="244">
         <f>SUM(N39-E53)</f>
         <v/>
       </c>
-      <c r="O53" s="243">
+      <c r="O53" s="244">
         <f>SUM(O39-F53)</f>
         <v/>
       </c>
-      <c r="P53" s="243">
+      <c r="P53" s="244">
         <f>SUM(P39-G53)</f>
         <v/>
       </c>
-      <c r="Q53" s="243">
+      <c r="Q53" s="244">
         <f>SUM(Q39-H53)</f>
         <v/>
       </c>
-      <c r="R53" s="243">
+      <c r="R53" s="244">
         <f>SUM(R39-I53)</f>
         <v/>
       </c>
-      <c r="S53" s="243">
+      <c r="S53" s="244">
         <f>SUM(S39-J53)</f>
         <v/>
       </c>
-      <c r="T53" s="244">
+      <c r="T53" s="245">
         <f>SUM(T39-K53)</f>
         <v/>
       </c>
@@ -6541,39 +6604,39 @@
       <c r="AD53" s="49" t="n"/>
       <c r="AE53" s="49" t="n"/>
       <c r="AF53" s="82" t="n"/>
-      <c r="AG53" s="242">
+      <c r="AG53" s="243">
         <f>SUM(AG39-X53)</f>
         <v/>
       </c>
-      <c r="AH53" s="243">
+      <c r="AH53" s="244">
         <f>SUM(AH39-Y53)</f>
         <v/>
       </c>
-      <c r="AI53" s="243">
+      <c r="AI53" s="244">
         <f>SUM(AI39-Z53)</f>
         <v/>
       </c>
-      <c r="AJ53" s="243">
+      <c r="AJ53" s="244">
         <f>SUM(AJ39-AA53)</f>
         <v/>
       </c>
-      <c r="AK53" s="243">
+      <c r="AK53" s="244">
         <f>SUM(AK39-AB53)</f>
         <v/>
       </c>
-      <c r="AL53" s="243">
+      <c r="AL53" s="244">
         <f>SUM(AL39-AC53)</f>
         <v/>
       </c>
-      <c r="AM53" s="243">
+      <c r="AM53" s="244">
         <f>SUM(AM39-AD53)</f>
         <v/>
       </c>
-      <c r="AN53" s="243">
+      <c r="AN53" s="244">
         <f>SUM(AN39-AE53)</f>
         <v/>
       </c>
-      <c r="AO53" s="244">
+      <c r="AO53" s="245">
         <f>SUM(AO39-AF53)</f>
         <v/>
       </c>
@@ -6594,39 +6657,39 @@
       <c r="I54" s="85" t="n"/>
       <c r="J54" s="85" t="n"/>
       <c r="K54" s="86" t="n"/>
-      <c r="L54" s="245">
+      <c r="L54" s="246">
         <f>SUM(L40-C54)</f>
         <v/>
       </c>
-      <c r="M54" s="246">
+      <c r="M54" s="247">
         <f>SUM(M40-D54)</f>
         <v/>
       </c>
-      <c r="N54" s="246">
+      <c r="N54" s="247">
         <f>SUM(N40-E54)</f>
         <v/>
       </c>
-      <c r="O54" s="246">
+      <c r="O54" s="247">
         <f>SUM(O40-F54)</f>
         <v/>
       </c>
-      <c r="P54" s="246">
+      <c r="P54" s="247">
         <f>SUM(P40-G54)</f>
         <v/>
       </c>
-      <c r="Q54" s="246">
+      <c r="Q54" s="247">
         <f>SUM(Q40-H54)</f>
         <v/>
       </c>
-      <c r="R54" s="246">
+      <c r="R54" s="247">
         <f>SUM(R40-I54)</f>
         <v/>
       </c>
-      <c r="S54" s="246">
+      <c r="S54" s="247">
         <f>SUM(S40-J54)</f>
         <v/>
       </c>
-      <c r="T54" s="247">
+      <c r="T54" s="248">
         <f>SUM(T40-K54)</f>
         <v/>
       </c>
@@ -6646,39 +6709,39 @@
       <c r="AD54" s="85" t="n"/>
       <c r="AE54" s="85" t="n"/>
       <c r="AF54" s="86" t="n"/>
-      <c r="AG54" s="242">
+      <c r="AG54" s="243">
         <f>SUM(AG40-X54)</f>
         <v/>
       </c>
-      <c r="AH54" s="243">
+      <c r="AH54" s="244">
         <f>SUM(AH40-Y54)</f>
         <v/>
       </c>
-      <c r="AI54" s="243">
+      <c r="AI54" s="244">
         <f>SUM(AI40-Z54)</f>
         <v/>
       </c>
-      <c r="AJ54" s="243">
+      <c r="AJ54" s="244">
         <f>SUM(AJ40-AA54)</f>
         <v/>
       </c>
-      <c r="AK54" s="243">
+      <c r="AK54" s="244">
         <f>SUM(AK40-AB54)</f>
         <v/>
       </c>
-      <c r="AL54" s="243">
+      <c r="AL54" s="244">
         <f>SUM(AL40-AC54)</f>
         <v/>
       </c>
-      <c r="AM54" s="243">
+      <c r="AM54" s="244">
         <f>SUM(AM40-AD54)</f>
         <v/>
       </c>
-      <c r="AN54" s="243">
+      <c r="AN54" s="244">
         <f>SUM(AN40-AE54)</f>
         <v/>
       </c>
-      <c r="AO54" s="244">
+      <c r="AO54" s="245">
         <f>SUM(AO40-AF54)</f>
         <v/>
       </c>
@@ -6865,8 +6928,8 @@
   <mergeCells count="46">
     <mergeCell ref="V55:W55"/>
     <mergeCell ref="W59:AO59"/>
+    <mergeCell ref="AG2:AL2"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="AG2:AL2"/>
     <mergeCell ref="A2:B3"/>
     <mergeCell ref="W58:AO58"/>
     <mergeCell ref="I43:K43"/>
@@ -7405,39 +7468,39 @@
           <t>E/P In (this week)</t>
         </is>
       </c>
-      <c r="C4" s="251">
+      <c r="C4" s="252">
         <f>Daily!L14</f>
         <v/>
       </c>
-      <c r="D4" s="251">
+      <c r="D4" s="252">
         <f>Daily!M14</f>
         <v/>
       </c>
-      <c r="E4" s="251">
+      <c r="E4" s="252">
         <f>Daily!N14</f>
         <v/>
       </c>
-      <c r="F4" s="251">
+      <c r="F4" s="252">
         <f>Daily!O14</f>
         <v/>
       </c>
-      <c r="G4" s="251">
+      <c r="G4" s="252">
         <f>Daily!P14</f>
         <v/>
       </c>
-      <c r="H4" s="251">
+      <c r="H4" s="252">
         <f>Daily!Q14</f>
         <v/>
       </c>
-      <c r="I4" s="251">
+      <c r="I4" s="252">
         <f>Daily!R14</f>
         <v/>
       </c>
-      <c r="J4" s="251">
+      <c r="J4" s="252">
         <f>Daily!S14</f>
         <v/>
       </c>
-      <c r="K4" s="251">
+      <c r="K4" s="252">
         <f>Daily!T14</f>
         <v/>
       </c>
@@ -7472,39 +7535,39 @@
           <t>INBOUND MT RETURN</t>
         </is>
       </c>
-      <c r="C7" s="252">
+      <c r="C7" s="253">
         <f>Daily!C15</f>
         <v/>
       </c>
-      <c r="D7" s="252">
+      <c r="D7" s="253">
         <f>Daily!D15</f>
         <v/>
       </c>
-      <c r="E7" s="252">
+      <c r="E7" s="253">
         <f>Daily!E15</f>
         <v/>
       </c>
-      <c r="F7" s="252">
+      <c r="F7" s="253">
         <f>Daily!F15</f>
         <v/>
       </c>
-      <c r="G7" s="252">
+      <c r="G7" s="253">
         <f>Daily!G15</f>
         <v/>
       </c>
-      <c r="H7" s="252">
+      <c r="H7" s="253">
         <f>Daily!H15</f>
         <v/>
       </c>
-      <c r="I7" s="252">
+      <c r="I7" s="253">
         <f>Daily!I15</f>
         <v/>
       </c>
-      <c r="J7" s="252">
+      <c r="J7" s="253">
         <f>Daily!J15</f>
         <v/>
       </c>
-      <c r="K7" s="252">
+      <c r="K7" s="253">
         <f>Daily!K15</f>
         <v/>
       </c>
@@ -7515,39 +7578,39 @@
           <t>Booking(This week)</t>
         </is>
       </c>
-      <c r="C8" s="251">
+      <c r="C8" s="252">
         <f>Daily!C41</f>
         <v/>
       </c>
-      <c r="D8" s="251">
+      <c r="D8" s="252">
         <f>Daily!D41</f>
         <v/>
       </c>
-      <c r="E8" s="251">
+      <c r="E8" s="252">
         <f>Daily!E41</f>
         <v/>
       </c>
-      <c r="F8" s="251">
+      <c r="F8" s="252">
         <f>Daily!F41</f>
         <v/>
       </c>
-      <c r="G8" s="251">
+      <c r="G8" s="252">
         <f>Daily!G41</f>
         <v/>
       </c>
-      <c r="H8" s="251">
+      <c r="H8" s="252">
         <f>Daily!H41</f>
         <v/>
       </c>
-      <c r="I8" s="251">
+      <c r="I8" s="252">
         <f>Daily!I41</f>
         <v/>
       </c>
-      <c r="J8" s="251">
+      <c r="J8" s="252">
         <f>Daily!J41</f>
         <v/>
       </c>
-      <c r="K8" s="251">
+      <c r="K8" s="252">
         <f>Daily!K41</f>
         <v/>
       </c>
@@ -7562,39 +7625,39 @@
           <t>Booking(Next week)</t>
         </is>
       </c>
-      <c r="C9" s="253">
+      <c r="C9" s="254">
         <f>Daily!C55</f>
         <v/>
       </c>
-      <c r="D9" s="253">
+      <c r="D9" s="254">
         <f>Daily!D55</f>
         <v/>
       </c>
-      <c r="E9" s="253">
+      <c r="E9" s="254">
         <f>Daily!E55</f>
         <v/>
       </c>
-      <c r="F9" s="253">
+      <c r="F9" s="254">
         <f>Daily!F55</f>
         <v/>
       </c>
-      <c r="G9" s="253">
+      <c r="G9" s="254">
         <f>Daily!G55</f>
         <v/>
       </c>
-      <c r="H9" s="253">
+      <c r="H9" s="254">
         <f>Daily!H55</f>
         <v/>
       </c>
-      <c r="I9" s="253">
+      <c r="I9" s="254">
         <f>Daily!I55</f>
         <v/>
       </c>
-      <c r="J9" s="253">
+      <c r="J9" s="254">
         <f>Daily!J55</f>
         <v/>
       </c>
-      <c r="K9" s="253">
+      <c r="K9" s="254">
         <f>Daily!K55</f>
         <v/>
       </c>
@@ -7609,39 +7672,39 @@
           <t>Balance</t>
         </is>
       </c>
-      <c r="C10" s="254">
+      <c r="C10" s="255">
         <f>SUM(C3+C4+C5+C6+C7-C8-C9)</f>
         <v/>
       </c>
-      <c r="D10" s="254">
+      <c r="D10" s="255">
         <f>SUM(D3+D4+D5+D6+D7-D8-D9)</f>
         <v/>
       </c>
-      <c r="E10" s="254">
+      <c r="E10" s="255">
         <f>SUM(E3+E4+E5+E6+E7-E8-E9)</f>
         <v/>
       </c>
-      <c r="F10" s="254">
+      <c r="F10" s="255">
         <f>SUM(F3+F4+F5+F6+F7-F8-F9)</f>
         <v/>
       </c>
-      <c r="G10" s="255">
+      <c r="G10" s="256">
         <f>SUM(G3+G4+G5+G6+G7-G8-G9)</f>
         <v/>
       </c>
-      <c r="H10" s="255">
+      <c r="H10" s="256">
         <f>SUM(H3+H4+H5+H6+H7-H8-H9)</f>
         <v/>
       </c>
-      <c r="I10" s="255">
+      <c r="I10" s="256">
         <f>SUM(I3+I4+I5+I6+I7-I8-I9)</f>
         <v/>
       </c>
-      <c r="J10" s="255">
+      <c r="J10" s="256">
         <f>SUM(J3+J4+J5+J6+J7-J8-J9)</f>
         <v/>
       </c>
-      <c r="K10" s="255">
+      <c r="K10" s="256">
         <f>SUM(K3+K4+K5+K6+K7-K8-K9)</f>
         <v/>
       </c>
@@ -7775,39 +7838,39 @@
           <t>E/P In (this week)</t>
         </is>
       </c>
-      <c r="C15" s="251">
+      <c r="C15" s="252">
         <f>Daily!AG14</f>
         <v/>
       </c>
-      <c r="D15" s="251">
+      <c r="D15" s="252">
         <f>Daily!AH14</f>
         <v/>
       </c>
-      <c r="E15" s="251">
+      <c r="E15" s="252">
         <f>Daily!AI14</f>
         <v/>
       </c>
-      <c r="F15" s="251">
+      <c r="F15" s="252">
         <f>Daily!AJ14</f>
         <v/>
       </c>
-      <c r="G15" s="251">
+      <c r="G15" s="252">
         <f>Daily!AK14</f>
         <v/>
       </c>
-      <c r="H15" s="251">
+      <c r="H15" s="252">
         <f>Daily!AL14</f>
         <v/>
       </c>
-      <c r="I15" s="251">
+      <c r="I15" s="252">
         <f>Daily!AM14</f>
         <v/>
       </c>
-      <c r="J15" s="251">
+      <c r="J15" s="252">
         <f>Daily!AN14</f>
         <v/>
       </c>
-      <c r="K15" s="251">
+      <c r="K15" s="252">
         <f>Daily!AO14</f>
         <v/>
       </c>
@@ -7842,39 +7905,39 @@
           <t>INBOUND MT RETURN</t>
         </is>
       </c>
-      <c r="C18" s="252">
+      <c r="C18" s="253">
         <f>Daily!X15</f>
         <v/>
       </c>
-      <c r="D18" s="252">
+      <c r="D18" s="253">
         <f>Daily!Y15</f>
         <v/>
       </c>
-      <c r="E18" s="252">
+      <c r="E18" s="253">
         <f>Daily!Z15</f>
         <v/>
       </c>
-      <c r="F18" s="252">
+      <c r="F18" s="253">
         <f>Daily!AA15</f>
         <v/>
       </c>
-      <c r="G18" s="252">
+      <c r="G18" s="253">
         <f>Daily!AB15</f>
         <v/>
       </c>
-      <c r="H18" s="252">
+      <c r="H18" s="253">
         <f>Daily!AC15</f>
         <v/>
       </c>
-      <c r="I18" s="252">
+      <c r="I18" s="253">
         <f>Daily!AD15</f>
         <v/>
       </c>
-      <c r="J18" s="252">
+      <c r="J18" s="253">
         <f>Daily!AE15</f>
         <v/>
       </c>
-      <c r="K18" s="252">
+      <c r="K18" s="253">
         <f>Daily!AF15</f>
         <v/>
       </c>
@@ -7885,39 +7948,39 @@
           <t>Booking(This week)</t>
         </is>
       </c>
-      <c r="C19" s="253">
+      <c r="C19" s="254">
         <f>Daily!X41</f>
         <v/>
       </c>
-      <c r="D19" s="253">
+      <c r="D19" s="254">
         <f>Daily!Y41</f>
         <v/>
       </c>
-      <c r="E19" s="253">
+      <c r="E19" s="254">
         <f>Daily!Z41</f>
         <v/>
       </c>
-      <c r="F19" s="253">
+      <c r="F19" s="254">
         <f>Daily!AA41</f>
         <v/>
       </c>
-      <c r="G19" s="253">
+      <c r="G19" s="254">
         <f>Daily!AB41</f>
         <v/>
       </c>
-      <c r="H19" s="253">
+      <c r="H19" s="254">
         <f>Daily!AC41</f>
         <v/>
       </c>
-      <c r="I19" s="256">
+      <c r="I19" s="257">
         <f>Daily!AD41</f>
         <v/>
       </c>
-      <c r="J19" s="256">
+      <c r="J19" s="257">
         <f>Daily!AE41</f>
         <v/>
       </c>
-      <c r="K19" s="253">
+      <c r="K19" s="254">
         <f>Daily!AF41</f>
         <v/>
       </c>
@@ -7932,39 +7995,39 @@
           <t>Booking(Next week)</t>
         </is>
       </c>
-      <c r="C20" s="253">
+      <c r="C20" s="254">
         <f>Daily!X55</f>
         <v/>
       </c>
-      <c r="D20" s="253">
+      <c r="D20" s="254">
         <f>Daily!Y55</f>
         <v/>
       </c>
-      <c r="E20" s="253">
+      <c r="E20" s="254">
         <f>Daily!Z55</f>
         <v/>
       </c>
-      <c r="F20" s="253">
+      <c r="F20" s="254">
         <f>Daily!AA55</f>
         <v/>
       </c>
-      <c r="G20" s="253">
+      <c r="G20" s="254">
         <f>Daily!AB55</f>
         <v/>
       </c>
-      <c r="H20" s="253">
+      <c r="H20" s="254">
         <f>Daily!AC55</f>
         <v/>
       </c>
-      <c r="I20" s="253">
+      <c r="I20" s="254">
         <f>Daily!AD55</f>
         <v/>
       </c>
-      <c r="J20" s="253">
+      <c r="J20" s="254">
         <f>Daily!AE55</f>
         <v/>
       </c>
-      <c r="K20" s="253">
+      <c r="K20" s="254">
         <f>Daily!AF55</f>
         <v/>
       </c>
@@ -7979,39 +8042,39 @@
           <t>Balance</t>
         </is>
       </c>
-      <c r="C21" s="254">
+      <c r="C21" s="255">
         <f>SUM(C14+C15+C16+C17+C18-C19-C20)</f>
         <v/>
       </c>
-      <c r="D21" s="254">
+      <c r="D21" s="255">
         <f>SUM(D14+D15+D16+D17+D18-D19-D20)</f>
         <v/>
       </c>
-      <c r="E21" s="254">
+      <c r="E21" s="255">
         <f>SUM(E14+E15+E16+E17+E18-E19-E20)</f>
         <v/>
       </c>
-      <c r="F21" s="254">
+      <c r="F21" s="255">
         <f>SUM(F14+F15+F16+F17+F18-F19-F20)</f>
         <v/>
       </c>
-      <c r="G21" s="254">
+      <c r="G21" s="255">
         <f>SUM(G14+G15+G16+G17+G18-G19-G20)</f>
         <v/>
       </c>
-      <c r="H21" s="255">
+      <c r="H21" s="256">
         <f>SUM(H14+H15+H16+H17+H18-H19-H20)</f>
         <v/>
       </c>
-      <c r="I21" s="254">
+      <c r="I21" s="255">
         <f>SUM(I14+I15+I16+I17+I18-I19-I20)</f>
         <v/>
       </c>
-      <c r="J21" s="254">
+      <c r="J21" s="255">
         <f>SUM(J14+J15+J16+J17+J18-J19-J20)</f>
         <v/>
       </c>
-      <c r="K21" s="254">
+      <c r="K21" s="255">
         <f>SUM(K14+K15+K16+K17+K18-K19-K20)</f>
         <v/>
       </c>
